--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-procedurede-transport-patient.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-procedurede-transport-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$148</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4249" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5327" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1348,7 +1348,85 @@
     <t>Procedure.performer.extension</t>
   </si>
   <si>
-    <t>Procedure.performer.extension:transporteur</t>
+    <t>Procedure.performer.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.function</t>
+  </si>
+  <si>
+    <t>Type of performance</t>
+  </si>
+  <si>
+    <t>Distinguishes the type of involvement of the performer in the procedure. For example, surgeon, anaesthetist, endoscopist.</t>
+  </si>
+  <si>
+    <t>Allows disambiguation of the types of involvement of different performers.</t>
+  </si>
+  <si>
+    <t>A code that identifies the role of a performer of the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+  </si>
+  <si>
+    <t>Event.performer.function</t>
+  </si>
+  <si>
+    <t>.functionCode</t>
+  </si>
+  <si>
+    <t>Some combination of STF-18 / PRA-3 / PRT-4 / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17 / OBX-25</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+</t>
+  </si>
+  <si>
+    <t>The reference to the practitioner</t>
+  </si>
+  <si>
+    <t>The practitioner who was involved in the procedure.</t>
+  </si>
+  <si>
+    <t>A reference to Device supports use cases, such as pacemakers.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>.role</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>ORC-19/PRT-5</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur</t>
   </si>
   <si>
     <t>transporteur</t>
@@ -1364,46 +1442,46 @@
     <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
   </si>
   <si>
-    <t>Procedure.performer.extension:transporteur.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:type</t>
+    <t>Procedure.performer.actor.extension:transporteur.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:type</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>Procedure.performer.extension:transporteur.extension:type.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:type.url</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.extension.value[x]</t>
+    <t>Procedure.performer.actor.extension:transporteur.extension:type.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:type.url</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x]</t>
   </si>
   <si>
     <t>PRF</t>
@@ -1412,116 +1490,205 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
   </si>
   <si>
-    <t>Procedure.performer.extension:transporteur.extension:reference</t>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:typeCode.value[x].text</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:reference</t>
   </si>
   <si>
     <t>reference</t>
   </si>
   <si>
-    <t>Référence vers le rôle du praticien dans le document</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:reference.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:reference.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:reference.url</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension:transporteur.extension:reference.value[x]</t>
+    <t>Procedure.performer.actor.extension:transporteur.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension:transporteur.extension:reference.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
 </t>
   </si>
   <si>
-    <t>Procedure.performer.extension:transporteur.url</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.url</t>
+    <t>Procedure.performer.actor.extension:transporteur.url</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.url</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
-    <t>Procedure.performer.extension:transporteur.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.performer.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.function</t>
-  </si>
-  <si>
-    <t>Type of performance</t>
-  </si>
-  <si>
-    <t>Distinguishes the type of involvement of the performer in the procedure. For example, surgeon, anaesthetist, endoscopist.</t>
-  </si>
-  <si>
-    <t>Allows disambiguation of the types of involvement of different performers.</t>
-  </si>
-  <si>
-    <t>A code that identifies the role of a performer of the procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
-  </si>
-  <si>
-    <t>Event.performer.function</t>
-  </si>
-  <si>
-    <t>.functionCode</t>
-  </si>
-  <si>
-    <t>Some combination of STF-18 / PRA-3 / PRT-4 / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17 / OBX-25</t>
-  </si>
-  <si>
-    <t>Procedure.performer.actor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t>Procedure.performer.actor.extension:transporteur.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
 </t>
   </si>
   <si>
-    <t>The reference to the practitioner</t>
-  </si>
-  <si>
-    <t>The practitioner who was involved in the procedure.</t>
-  </si>
-  <si>
-    <t>A reference to Device supports use cases, such as pacemakers.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>.role</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>ORC-19/PRT-5</t>
+    <t>Procedure.performer.actor.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Procedure.performer.onBehalfOf</t>
@@ -1546,7 +1713,7 @@
     <t>Procedure.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-location-document)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -1563,6 +1730,53 @@
   </si>
   <si>
     <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>Procedure.location.id</t>
+  </si>
+  <si>
+    <t>Procedure.location.extension</t>
+  </si>
+  <si>
+    <t>Procedure.location.extension:lieuDepart</t>
+  </si>
+  <si>
+    <t>lieuDepart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-procedure-from-location}
+</t>
+  </si>
+  <si>
+    <t>Fr Lieu de départ du transport</t>
+  </si>
+  <si>
+    <t>Extension pour représenter le lieu de départ d’un transport (patient ou professionnel).</t>
+  </si>
+  <si>
+    <t>Procedure.location.extension:destination</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-procedure-to-location}
+</t>
+  </si>
+  <si>
+    <t>Extension pour représenter le lieu de destination d’un transport (patient ou professionnel).</t>
+  </si>
+  <si>
+    <t>Procedure.location.reference</t>
+  </si>
+  <si>
+    <t>Procedure.location.type</t>
+  </si>
+  <si>
+    <t>Procedure.location.identifier</t>
+  </si>
+  <si>
+    <t>Procedure.location.display</t>
   </si>
   <si>
     <t>Procedure.reasonCode</t>
@@ -2163,11 +2377,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN118"/>
+  <dimension ref="A1:AN148"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="71.54296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.7578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="80.14453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="61.6796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -11294,7 +11508,7 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11316,12 +11530,14 @@
         <v>132</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>133</v>
+        <v>234</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11358,14 +11574,16 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC81" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>237</v>
@@ -11386,7 +11604,7 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11400,41 +11618,43 @@
         <v>426</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C82" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+      <c r="N82" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11482,7 +11702,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>237</v>
+        <v>430</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11491,7 +11711,7 @@
         <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>138</v>
@@ -11500,7 +11720,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11514,7 +11734,7 @@
         <v>431</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11534,19 +11754,21 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>229</v>
+        <v>432</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>230</v>
+        <v>433</v>
       </c>
       <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11570,13 +11792,13 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -11594,7 +11816,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>231</v>
+        <v>431</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11606,27 +11828,27 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>232</v>
+        <v>438</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11634,10 +11856,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>292</v>
+        <v>87</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -11646,19 +11868,21 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>132</v>
+        <v>441</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>133</v>
+        <v>442</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>134</v>
+        <v>443</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
       </c>
@@ -11694,61 +11918,59 @@
         <v>77</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>237</v>
+        <v>440</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>77</v>
+        <v>445</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>77</v>
+        <v>446</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>87</v>
@@ -11763,13 +11985,13 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>134</v>
+        <v>230</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11820,25 +12042,25 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -11849,10 +12071,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11860,10 +12082,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -11875,13 +12097,13 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>229</v>
+        <v>133</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11920,37 +12142,37 @@
         <v>77</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11961,21 +12183,23 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
@@ -11987,13 +12211,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>132</v>
+        <v>453</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>133</v>
+        <v>454</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>134</v>
+        <v>455</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12032,16 +12256,16 @@
         <v>77</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>237</v>
@@ -12073,10 +12297,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12084,7 +12308,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>87</v>
@@ -12099,24 +12323,22 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>436</v>
+        <v>77</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>77</v>
@@ -12158,10 +12380,10 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>87</v>
@@ -12176,7 +12398,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12187,10 +12409,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12198,10 +12420,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>77</v>
@@ -12213,13 +12435,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>271</v>
+        <v>133</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12228,7 +12450,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>445</v>
+        <v>77</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>77</v>
@@ -12246,47 +12468,49 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y89" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z89" t="s" s="2">
-        <v>446</v>
+        <v>77</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12297,13 +12521,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>77</v>
@@ -12328,7 +12552,7 @@
         <v>132</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>449</v>
+        <v>133</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>134</v>
@@ -12411,10 +12635,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12523,10 +12747,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12635,10 +12859,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12678,7 +12902,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>77</v>
@@ -12749,10 +12973,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12775,7 +12999,7 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>454</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>271</v>
@@ -12790,7 +13014,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>77</v>
+        <v>470</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>77</v>
@@ -12808,13 +13032,11 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>77</v>
+        <v>471</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -12861,18 +13083,20 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>87</v>
@@ -12887,24 +13111,22 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>457</v>
+        <v>77</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>77</v>
@@ -12946,25 +13168,25 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12975,10 +13197,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12989,7 +13211,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
@@ -13001,13 +13223,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>271</v>
+        <v>229</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>272</v>
+        <v>230</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13058,7 +13280,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13070,13 +13292,13 @@
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -13087,46 +13309,42 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>462</v>
+        <v>133</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
@@ -13162,19 +13380,19 @@
         <v>77</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>464</v>
+        <v>237</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13192,7 +13410,7 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -13203,10 +13421,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13214,7 +13432,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>87</v>
@@ -13226,27 +13444,27 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>466</v>
+        <v>265</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>77</v>
+        <v>473</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>77</v>
@@ -13264,13 +13482,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>470</v>
+        <v>77</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -13288,10 +13506,10 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>465</v>
+        <v>268</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>87</v>
@@ -13300,27 +13518,27 @@
         <v>77</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>471</v>
+        <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>472</v>
+        <v>130</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>473</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13328,7 +13546,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>87</v>
@@ -13340,21 +13558,19 @@
         <v>77</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>475</v>
+        <v>200</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>476</v>
+        <v>271</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>477</v>
+        <v>272</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>478</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>77</v>
       </c>
@@ -13402,10 +13618,10 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>474</v>
+        <v>274</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>87</v>
@@ -13417,24 +13633,24 @@
         <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13457,18 +13673,16 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>484</v>
+        <v>228</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>485</v>
+        <v>229</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>486</v>
+        <v>230</v>
       </c>
       <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>487</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
       </c>
@@ -13516,7 +13730,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>483</v>
+        <v>231</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13528,13 +13742,13 @@
         <v>77</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>488</v>
+        <v>232</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -13545,44 +13759,44 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>490</v>
+        <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>491</v>
+        <v>234</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
       </c>
@@ -13618,40 +13832,40 @@
         <v>77</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>489</v>
+        <v>237</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>494</v>
+        <v>232</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>495</v>
+        <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>77</v>
@@ -13659,10 +13873,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13685,18 +13899,20 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>497</v>
+        <v>240</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>498</v>
+        <v>241</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
       </c>
@@ -13720,13 +13936,13 @@
         <v>77</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>500</v>
+        <v>77</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>501</v>
+        <v>77</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>77</v>
@@ -13744,7 +13960,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>496</v>
+        <v>244</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13759,24 +13975,24 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>503</v>
+        <v>245</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>504</v>
+        <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13787,7 +14003,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>77</v>
@@ -13796,20 +14012,18 @@
         <v>77</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>506</v>
+        <v>228</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>507</v>
+        <v>229</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13858,28 +14072,28 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>505</v>
+        <v>231</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>510</v>
+        <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>503</v>
+        <v>232</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>504</v>
+        <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>77</v>
@@ -13887,14 +14101,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -13910,19 +14124,19 @@
         <v>77</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>512</v>
+        <v>234</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>513</v>
+        <v>235</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>514</v>
+        <v>149</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13948,31 +14162,31 @@
         <v>77</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>515</v>
+        <v>77</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>516</v>
+        <v>77</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>511</v>
+        <v>237</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13984,27 +14198,27 @@
         <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>517</v>
+        <v>232</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>518</v>
+        <v>77</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>519</v>
+        <v>489</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14027,18 +14241,20 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>520</v>
+        <v>316</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>521</v>
+        <v>317</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
       </c>
@@ -14062,13 +14278,13 @@
         <v>77</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>523</v>
+        <v>77</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>524</v>
+        <v>77</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>77</v>
@@ -14086,7 +14302,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>519</v>
+        <v>321</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14104,21 +14320,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>525</v>
+        <v>322</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>77</v>
+        <v>323</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>526</v>
+        <v>490</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>526</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14129,7 +14345,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>77</v>
@@ -14138,19 +14354,19 @@
         <v>77</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>527</v>
+        <v>228</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>528</v>
+        <v>326</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>529</v>
+        <v>327</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>530</v>
+        <v>328</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14200,13 +14416,13 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>526</v>
+        <v>329</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>77</v>
@@ -14218,21 +14434,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>531</v>
+        <v>330</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>77</v>
+        <v>331</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>532</v>
+        <v>492</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14243,7 +14459,7 @@
         <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>77</v>
@@ -14252,21 +14468,21 @@
         <v>77</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>533</v>
+        <v>334</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
       </c>
@@ -14275,7 +14491,7 @@
         <v>77</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>77</v>
+        <v>470</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>77</v>
@@ -14290,13 +14506,13 @@
         <v>77</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>536</v>
+        <v>77</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>537</v>
+        <v>77</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>77</v>
@@ -14314,13 +14530,13 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>532</v>
+        <v>337</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>77</v>
@@ -14332,21 +14548,21 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>538</v>
+        <v>338</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>539</v>
+        <v>494</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>539</v>
+        <v>495</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14357,7 +14573,7 @@
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>77</v>
@@ -14366,20 +14582,20 @@
         <v>77</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>540</v>
+        <v>228</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>541</v>
+        <v>342</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>542</v>
+        <v>343</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>543</v>
+        <v>344</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -14428,13 +14644,13 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>539</v>
+        <v>345</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>77</v>
@@ -14446,21 +14662,21 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>538</v>
+        <v>346</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>544</v>
+        <v>496</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14471,7 +14687,7 @@
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>77</v>
@@ -14480,19 +14696,23 @@
         <v>77</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>545</v>
+        <v>351</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
       </c>
@@ -14516,13 +14736,13 @@
         <v>77</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>547</v>
+        <v>77</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>548</v>
+        <v>77</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>77</v>
@@ -14540,13 +14760,13 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>544</v>
+        <v>355</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>77</v>
@@ -14558,21 +14778,21 @@
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>549</v>
+        <v>356</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>550</v>
+        <v>498</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14583,7 +14803,7 @@
         <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>77</v>
@@ -14592,19 +14812,23 @@
         <v>77</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>551</v>
+        <v>228</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>552</v>
+        <v>360</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
       </c>
@@ -14652,13 +14876,13 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>550</v>
+        <v>364</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>77</v>
@@ -14667,35 +14891,37 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>554</v>
+        <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>555</v>
+        <v>365</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>556</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>557</v>
+        <v>500</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>77</v>
@@ -14707,13 +14933,13 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>419</v>
+        <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>558</v>
+        <v>133</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>559</v>
+        <v>134</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14764,7 +14990,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>557</v>
+        <v>237</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14776,13 +15002,13 @@
         <v>77</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>560</v>
+        <v>77</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
@@ -14793,10 +15019,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>561</v>
+        <v>502</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>561</v>
+        <v>463</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14905,21 +15131,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>562</v>
+        <v>465</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>77</v>
@@ -14934,14 +15160,12 @@
         <v>132</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14978,16 +15202,16 @@
         <v>77</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>237</v>
@@ -15008,7 +15232,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -15019,52 +15243,50 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>563</v>
+        <v>504</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>563</v>
+        <v>467</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>462</v>
+        <v>265</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>463</v>
+        <v>266</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>77</v>
+        <v>501</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>77</v>
@@ -15106,19 +15328,19 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>464</v>
+        <v>268</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>77</v>
@@ -15135,10 +15357,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>564</v>
+        <v>469</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15161,13 +15383,13 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>200</v>
+        <v>506</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>565</v>
+        <v>271</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>566</v>
+        <v>272</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15194,13 +15416,13 @@
         <v>77</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>567</v>
+        <v>77</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>568</v>
+        <v>77</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>77</v>
@@ -15218,7 +15440,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>564</v>
+        <v>274</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15236,7 +15458,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>569</v>
+        <v>130</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -15247,10 +15469,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>570</v>
+        <v>507</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>570</v>
+        <v>508</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15273,22 +15495,24 @@
         <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>571</v>
+        <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>572</v>
+        <v>265</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>77</v>
+        <v>509</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>77</v>
@@ -15330,7 +15554,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>570</v>
+        <v>268</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>87</v>
@@ -15342,13 +15566,13 @@
         <v>77</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>574</v>
+        <v>130</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15359,10 +15583,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>575</v>
+        <v>511</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15373,7 +15597,7 @@
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>77</v>
@@ -15385,20 +15609,16 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>576</v>
+        <v>287</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>577</v>
+        <v>271</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>77</v>
       </c>
@@ -15446,13 +15666,13 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>575</v>
+        <v>274</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>77</v>
@@ -15464,7 +15684,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>581</v>
+        <v>130</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15475,10 +15695,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>582</v>
+        <v>512</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>582</v>
+        <v>512</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15489,7 +15709,7 @@
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>77</v>
@@ -15498,19 +15718,19 @@
         <v>77</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>583</v>
+        <v>513</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>584</v>
+        <v>514</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>579</v>
+        <v>515</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15536,13 +15756,13 @@
         <v>77</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>585</v>
+        <v>77</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>586</v>
+        <v>77</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>77</v>
@@ -15560,16 +15780,16 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>582</v>
+        <v>516</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>77</v>
+        <v>517</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>99</v>
@@ -15578,17 +15798,3427 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AM118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN118" t="s" s="2">
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="P147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN148" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN118">
+  <autoFilter ref="A1:AN148">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15598,7 +19228,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI117">
+  <conditionalFormatting sqref="A2:AI147">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
